--- a/mainWidget/mainWidget/src/database/防隔热材料.xlsx
+++ b/mainWidget/mainWidget/src/database/防隔热材料.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\gfapp_new\gfapp\mainWidget\mainWidget\src\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD6C16E-6128-4EB4-B733-7083F8202910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF117BF-7AAA-495D-89B4-4C0B5FD43728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,7 +112,21 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>杨氏模量</t>
+      <t>泊松比</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>屈服强度</t>
     </r>
     <r>
       <rPr>
@@ -122,7 +136,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[Pa]</t>
+      <t>[MPa]</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -136,21 +150,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>泊松比</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>屈服强度</t>
+      <t>抗拉强度</t>
     </r>
     <r>
       <rPr>
@@ -174,7 +174,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>抗拉强度</t>
+      <t>热导率</t>
     </r>
     <r>
       <rPr>
@@ -184,7 +184,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[MPa]</t>
+      <t>[W/m K]</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -198,7 +198,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>热导率</t>
+      <t>比热容</t>
     </r>
     <r>
       <rPr>
@@ -208,56 +208,63 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[W/m K]</t>
+      <t>[J/kg K]</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>比热容</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>玻璃纤维增强环氧树脂</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>芳纶纤维增强环氧树脂</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碳纤维增强环氧树脂（</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[J/kg K]</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>玻璃纤维增强环氧树脂</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>芳纶纤维增强环氧树脂</t>
+      <t>T300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
     </r>
   </si>
   <si>
@@ -278,7 +285,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>T300</t>
+      <t>T700</t>
     </r>
     <r>
       <rPr>
@@ -309,7 +316,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>T700</t>
+      <t>M40</t>
     </r>
     <r>
       <rPr>
@@ -331,111 +338,104 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>碳纤维增强环氧树脂（</t>
-    </r>
-    <r>
-      <rPr>
+      <t>硼纤维增强环氧树脂</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>石英纤维增强环氧树脂</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>硅橡胶隔热材料</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>氟橡胶隔热材料</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三元乙丙橡胶隔热材料</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>氧化铝纤维隔热材料</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>氮化硼纤维隔热材料</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>杨氏模量</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>M40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>硼纤维增强环氧树脂</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>石英纤维增强环氧树脂</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>硅橡胶隔热材料</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>氟橡胶隔热材料</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>三元乙丙橡胶隔热材料</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>氧化铝纤维隔热材料</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>氮化硼纤维隔热材料</t>
-    </r>
+      <t>[GPa]</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -446,7 +446,7 @@
     <numFmt numFmtId="176" formatCode="0;[Red]0"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,6 +486,14 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="仿宋"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -568,15 +576,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -603,6 +608,13 @@
     <xf numFmtId="177" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -885,6 +897,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="15.5" style="13" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.45" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
@@ -899,406 +914,406 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="7">
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="6">
         <v>1800</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="E2" s="8">
-        <v>6000000000</v>
-      </c>
-      <c r="F2" s="7">
+      <c r="E2" s="12">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6">
         <v>0.3</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <v>60</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="9">
         <v>90</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0.5</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <v>1300</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="7">
+      <c r="B3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6">
         <v>1400</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="E3" s="8">
-        <v>10000000000</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="E3" s="12">
+        <v>10</v>
+      </c>
+      <c r="F3" s="6">
         <v>0.25</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>100</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <v>150</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="10">
         <v>0.3</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <v>1400</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="7">
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6">
         <v>1750</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="E4" s="8">
-        <v>24000000000</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E4" s="12">
+        <v>24</v>
+      </c>
+      <c r="F4" s="6">
         <v>0.17</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="8">
         <v>133</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>200</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="10">
         <v>1</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <v>1100</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="7">
+      <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6">
         <v>1900</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>3.0000000000000001E-6</v>
       </c>
-      <c r="E5" s="8">
-        <v>29000000000</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E5" s="12">
+        <v>29</v>
+      </c>
+      <c r="F5" s="6">
         <v>0.16</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>200</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <v>300</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="10">
         <v>1.2</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="6">
         <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="7">
+      <c r="B6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="6">
         <v>2000</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>1.9999999999999999E-6</v>
       </c>
-      <c r="E6" s="8">
-        <v>38000000000</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="E6" s="12">
+        <v>38</v>
+      </c>
+      <c r="F6" s="6">
         <v>0.14000000000000001</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>233</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <v>350</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="10">
         <v>1.5</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="6">
         <v>950</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="B7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="6">
         <v>2200</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>3.0000000000000001E-6</v>
       </c>
-      <c r="E7" s="8">
-        <v>30000000000</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E7" s="12">
+        <v>30</v>
+      </c>
+      <c r="F7" s="6">
         <v>0.15</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>200</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <v>300</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="10">
         <v>1.3</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="6">
         <v>900</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="7">
+      <c r="B8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="6">
         <v>1900</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="E8" s="8">
-        <v>6000000000</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E8" s="12">
+        <v>6</v>
+      </c>
+      <c r="F8" s="6">
         <v>0.25</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>66</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <v>100</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="10">
         <v>0.4</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="6">
         <v>1250</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="B9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="6">
         <v>1300</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="E9" s="8">
-        <v>100000</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="12">
+        <v>1E-4</v>
+      </c>
+      <c r="F9" s="6">
         <v>0.45</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>3</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <v>5</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="10">
         <v>0.3</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="6">
         <v>1400</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="6">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6">
         <v>1500</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>1.5E-5</v>
       </c>
-      <c r="E10" s="8">
-        <v>200000</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="E10" s="12">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F10" s="6">
         <v>0.45</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>5</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <v>8</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="10">
         <v>0.35</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="6">
         <v>1300</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6">
         <v>1200</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="E11" s="8">
-        <v>100000</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E11" s="12">
+        <v>1E-4</v>
+      </c>
+      <c r="F11" s="6">
         <v>0.45</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>6</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <v>6</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="10">
         <v>0.3</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="6">
         <v>1450</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="6">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="7">
+      <c r="B12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="6">
         <v>400</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>1.5E-5</v>
       </c>
-      <c r="E12" s="8">
-        <v>2500000</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E12" s="12">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="F12" s="6">
         <v>0.25</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <v>8</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <v>12</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="6">
         <v>900</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="6">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="7">
+      <c r="B13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="6">
         <v>2200</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="E13" s="8">
-        <v>15000000000</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E13" s="12">
+        <v>15</v>
+      </c>
+      <c r="F13" s="6">
         <v>0.2</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <v>100</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <v>150</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="10">
         <v>3</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="6">
         <v>850</v>
       </c>
     </row>

--- a/mainWidget/mainWidget/src/database/防隔热材料.xlsx
+++ b/mainWidget/mainWidget/src/database/防隔热材料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF117BF-7AAA-495D-89B4-4C0B5FD43728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84A46F3-8302-48C9-AA86-A7AE0B1657A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="76">
   <si>
     <r>
       <rPr>
@@ -435,6 +435,222 @@
       </rPr>
       <t>[GPa]</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>133</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>350</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>950</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>66</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>850</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000015</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -442,10 +658,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0;[Red]0"/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
-  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -576,18 +788,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -596,25 +802,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -898,7 +1101,9 @@
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="15.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="10"/>
+    <col min="5" max="5" width="15.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="9.140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -911,410 +1116,410 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="4">
         <v>1800</v>
       </c>
-      <c r="D2" s="7">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="E2" s="12">
-        <v>6</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="G2" s="8">
-        <v>60</v>
-      </c>
-      <c r="H2" s="9">
-        <v>90</v>
-      </c>
-      <c r="I2" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="J2" s="6">
-        <v>1300</v>
+      <c r="D2" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="5">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="4">
         <v>1400</v>
       </c>
-      <c r="D3" s="7">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="E3" s="12">
-        <v>10</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="G3" s="8">
-        <v>100</v>
-      </c>
-      <c r="H3" s="9">
-        <v>150</v>
-      </c>
-      <c r="I3" s="10">
+      <c r="D3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="8">
         <v>0.3</v>
       </c>
-      <c r="J3" s="6">
-        <v>1400</v>
+      <c r="J3" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>1750</v>
       </c>
-      <c r="D4" s="7">
-        <v>5.0000000000000004E-6</v>
-      </c>
-      <c r="E4" s="12">
-        <v>24</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0.17</v>
-      </c>
-      <c r="G4" s="8">
-        <v>133</v>
-      </c>
-      <c r="H4" s="9">
-        <v>200</v>
-      </c>
-      <c r="I4" s="10">
-        <v>1</v>
-      </c>
-      <c r="J4" s="6">
-        <v>1100</v>
+      <c r="D4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="5">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>1900</v>
       </c>
-      <c r="D5" s="7">
-        <v>3.0000000000000001E-6</v>
-      </c>
-      <c r="E5" s="12">
-        <v>29</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="G5" s="8">
-        <v>200</v>
-      </c>
-      <c r="H5" s="9">
-        <v>300</v>
-      </c>
-      <c r="I5" s="10">
-        <v>1.2</v>
-      </c>
-      <c r="J5" s="6">
-        <v>1000</v>
+      <c r="D5" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="5">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>2000</v>
       </c>
-      <c r="D6" s="7">
-        <v>1.9999999999999999E-6</v>
-      </c>
-      <c r="E6" s="12">
-        <v>38</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G6" s="8">
+      <c r="D6" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="9">
         <v>233</v>
       </c>
-      <c r="H6" s="9">
-        <v>350</v>
-      </c>
-      <c r="I6" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="J6" s="6">
-        <v>950</v>
+      <c r="H6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="5">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>2200</v>
       </c>
-      <c r="D7" s="7">
-        <v>3.0000000000000001E-6</v>
-      </c>
-      <c r="E7" s="12">
-        <v>30</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0.15</v>
-      </c>
-      <c r="G7" s="8">
-        <v>200</v>
-      </c>
-      <c r="H7" s="9">
-        <v>300</v>
-      </c>
-      <c r="I7" s="10">
-        <v>1.3</v>
-      </c>
-      <c r="J7" s="6">
-        <v>900</v>
+      <c r="D7" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="5">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>1900</v>
       </c>
-      <c r="D8" s="7">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="E8" s="12">
-        <v>6</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="G8" s="8">
-        <v>66</v>
-      </c>
-      <c r="H8" s="9">
+      <c r="D8" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="8">
         <v>100</v>
       </c>
-      <c r="I8" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="J8" s="6">
-        <v>1250</v>
+      <c r="I8" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="5">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <v>1300</v>
       </c>
-      <c r="D9" s="7">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="E9" s="12">
-        <v>1E-4</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0.45</v>
-      </c>
-      <c r="G9" s="8">
-        <v>3</v>
-      </c>
-      <c r="H9" s="9">
-        <v>5</v>
-      </c>
-      <c r="I9" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="J9" s="6">
-        <v>1400</v>
+      <c r="D9" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="5">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>1500</v>
       </c>
-      <c r="D10" s="7">
-        <v>1.5E-5</v>
-      </c>
-      <c r="E10" s="12">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0.45</v>
-      </c>
-      <c r="G10" s="8">
-        <v>5</v>
-      </c>
-      <c r="H10" s="9">
-        <v>8</v>
-      </c>
-      <c r="I10" s="10">
-        <v>0.35</v>
-      </c>
-      <c r="J10" s="6">
-        <v>1300</v>
+      <c r="D10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="5">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
         <v>1200</v>
       </c>
-      <c r="D11" s="7">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="E11" s="12">
-        <v>1E-4</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0.45</v>
-      </c>
-      <c r="G11" s="8">
-        <v>6</v>
-      </c>
-      <c r="H11" s="9">
-        <v>6</v>
-      </c>
-      <c r="I11" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="J11" s="6">
-        <v>1450</v>
+      <c r="D11" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="5">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>400</v>
       </c>
-      <c r="D12" s="7">
-        <v>1.5E-5</v>
-      </c>
-      <c r="E12" s="12">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="8">
-        <v>8</v>
-      </c>
-      <c r="H12" s="9">
-        <v>12</v>
-      </c>
-      <c r="I12" s="10">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="J12" s="6">
-        <v>900</v>
+      <c r="D12" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="5">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="4">
         <v>2200</v>
       </c>
-      <c r="D13" s="7">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="E13" s="12">
-        <v>15</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="G13" s="8">
-        <v>100</v>
-      </c>
-      <c r="H13" s="9">
-        <v>150</v>
-      </c>
-      <c r="I13" s="10">
-        <v>3</v>
-      </c>
-      <c r="J13" s="6">
-        <v>850</v>
+      <c r="D13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/mainWidget/mainWidget/src/database/防隔热材料.xlsx
+++ b/mainWidget/mainWidget/src/database/防隔热材料.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84A46F3-8302-48C9-AA86-A7AE0B1657A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="75">
   <si>
     <r>
       <rPr>
@@ -414,6 +408,186 @@
     </r>
   </si>
   <si>
+    <t>6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>133</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>350</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>950</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>66</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>850</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -433,231 +607,47 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[GPa]</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>60</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.17</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>133</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>29</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>38</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>350</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>950</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>66</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>850</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.07</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1450</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000015</t>
+      <t>[MPa]</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1090,14 +1080,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1120,7 +1110,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>4</v>
@@ -1149,25 +1139,25 @@
         <v>1800</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1181,25 +1171,25 @@
         <v>1400</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I3" s="8">
         <v>0.3</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
@@ -1213,25 +1203,25 @@
         <v>1750</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
@@ -1245,25 +1235,25 @@
         <v>1900</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
@@ -1277,25 +1267,25 @@
         <v>2000</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G6" s="9">
         <v>233</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1309,25 +1299,25 @@
         <v>2200</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1341,25 +1331,25 @@
         <v>1900</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H8" s="8">
         <v>100</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1373,25 +1363,25 @@
         <v>1300</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1405,25 +1395,25 @@
         <v>1500</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1437,25 +1427,25 @@
         <v>1200</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>24</v>
-      </c>
       <c r="J11" s="8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1469,25 +1459,25 @@
         <v>400</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1501,25 +1491,25 @@
         <v>2200</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
